--- a/source/Part_02_Excel/M1/tasks/pre_0/a/solution.xlsx
+++ b/source/Part_02_Excel/M1/tasks/pre_0/a/solution.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\Personal\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lewil\Box\Main Pathway Redesign\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F2E1E4E2-ADD8-4DE9-888A-B76CCE59D8AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23658186-2F2D-4ED4-8465-0D1483549905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16320" yWindow="-2895" windowWidth="16440" windowHeight="28320" xr2:uid="{DEDA1C8B-1553-4801-B352-B17DEFC5138D}"/>
+    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DEDA1C8B-1553-4801-B352-B17DEFC5138D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="28">
   <si>
     <t>ENGR 131</t>
   </si>
@@ -51,9 +51,6 @@
   </si>
   <si>
     <t>login@purdue.edu</t>
-  </si>
-  <si>
-    <t>Student Name</t>
   </si>
   <si>
     <t>PCA01</t>
@@ -104,32 +101,32 @@
     <t>Number of Days:</t>
   </si>
   <si>
-    <t>header</t>
-  </si>
-  <si>
-    <t>header2</t>
-  </si>
-  <si>
     <t>Energy Conversion</t>
-  </si>
-  <si>
-    <t>Energy (kWh)</t>
-  </si>
-  <si>
-    <t>Energy (J)</t>
   </si>
   <si>
     <t>Performance Adjustment Factor</t>
   </si>
   <si>
-    <t>Adjusted Energy (kWh)</t>
+    <t>SOLUTION</t>
+  </si>
+  <si>
+    <t>* can use either column F or E for count</t>
+  </si>
+  <si>
+    <t>Energy Usage (kWh)</t>
+  </si>
+  <si>
+    <t>Adjusted Energy Usage (kWh)</t>
+  </si>
+  <si>
+    <t>Energy Usage (J)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -163,6 +160,21 @@
       <family val="2"/>
       <scheme val="major"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFC00000"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFC00000"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -184,7 +196,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -306,21 +318,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -334,23 +337,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -359,122 +350,27 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="2"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="3" tint="0.89999084444715716"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -487,14 +383,2108 @@
 </styleSheet>
 </file>
 
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0A2B6826-DC59-4750-922B-68A3BFDBA1BB}" name="Table1" displayName="Table1" ref="E6:F13" totalsRowShown="0" headerRowDxfId="4" headerRowBorderDxfId="3" tableBorderDxfId="2">
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{D4A9AFA8-4B39-4201-A9CE-DB6B0C5ADA58}" name="header" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{DC320AFE-0C9C-46C6-BA36-7056BA730529}" name="header2" dataDxfId="0"/>
-  </tableColumns>
-  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Laboratory Power</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> Usage Data</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$H$23</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Adjusted Energy Usage (kWh)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$E$24:$E$30</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Monday</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Tuesday</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Wednesday</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Thursday</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Friday</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Saturday</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Sunday</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$H$24:$H$30</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>129.60000000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>145.80000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>138.24</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>153.36000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>124.2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>105.84</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>120.96000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5573-4284-9390-97EAC3F4F670}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1995377887"/>
+        <c:axId val="1995376927"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1995377887"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Day</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1995376927"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1995376927"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+                  <a:lnSpc>
+                    <a:spcPct val="100000"/>
+                  </a:lnSpc>
+                  <a:spcBef>
+                    <a:spcPts val="0"/>
+                  </a:spcBef>
+                  <a:spcAft>
+                    <a:spcPts val="0"/>
+                  </a:spcAft>
+                  <a:buClrTx/>
+                  <a:buSzTx/>
+                  <a:buFontTx/>
+                  <a:buNone/>
+                  <a:tabLst/>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Adjusted Energy Usage (kWh)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+                <a:lnSpc>
+                  <a:spcPct val="100000"/>
+                </a:lnSpc>
+                <a:spcBef>
+                  <a:spcPts val="0"/>
+                </a:spcBef>
+                <a:spcAft>
+                  <a:spcPts val="0"/>
+                </a:spcAft>
+                <a:buClrTx/>
+                <a:buSzTx/>
+                <a:buFontTx/>
+                <a:buNone/>
+                <a:tabLst/>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:sysClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1995377887"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Laboratory Power Usage Data</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$H$23</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Adjusted Energy Usage (kWh)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$E$24:$E$30</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Monday</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Tuesday</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Wednesday</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Thursday</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Friday</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Saturday</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Sunday</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$H$24:$H$30</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>129.60000000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>145.80000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>138.24</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>153.36000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>124.2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>105.84</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>120.96000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E5FA-4DF8-BDE5-DDB9A8DDEFF1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="2012400543"/>
+        <c:axId val="2012399103"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="2012400543"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Day</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2012399103"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2012399103"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Adjusted Energy Usage (kWh)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2012400543"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>473075</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>561975</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E1F9BF2-50DF-F637-7FCC-5FF02CFD08DB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>484187</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>655637</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B686A0C4-9C53-6705-88EC-F6922C64C7D0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -814,270 +2804,318 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B39A92BC-BA68-4245-945E-9865DEE309B0}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A2:H30"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.84375" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="14" style="2" customWidth="1"/>
-    <col min="2" max="4" width="8.88671875" style="2"/>
-    <col min="5" max="5" width="19.5546875" style="2" customWidth="1"/>
-    <col min="6" max="7" width="14.33203125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="27.109375" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="2"/>
+    <col min="2" max="4" width="8.84375" style="2"/>
+    <col min="5" max="5" width="19.53515625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="18.61328125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="14.3046875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="25.69140625" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="8.84375" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>7</v>
-      </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>5</v>
+      <c r="B5" s="18" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="26" t="s">
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="E7" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="8">
+        <v>120</v>
+      </c>
+      <c r="H7" s="17">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="E8" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="9">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="E9" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="9">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="E10" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="9">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="E11" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="9">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="E12" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="9">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="E13" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="10">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="E15" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="E16" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="19">
+        <f>SUM(F7:F13)</f>
+        <v>850</v>
+      </c>
+    </row>
+    <row r="17" spans="5:8" x14ac:dyDescent="0.4">
+      <c r="E17" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="22">
+        <f>AVERAGE(F7:F13)</f>
+        <v>121.42857142857143</v>
+      </c>
+    </row>
+    <row r="18" spans="5:8" x14ac:dyDescent="0.4">
+      <c r="E18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" s="22">
+        <f>MAX(F7:F13)</f>
+        <v>142</v>
+      </c>
+    </row>
+    <row r="19" spans="5:8" x14ac:dyDescent="0.4">
+      <c r="E19" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" s="22">
+        <f>MIN(F7:F13)</f>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="20" spans="5:8" x14ac:dyDescent="0.4">
+      <c r="E20" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F20" s="23">
+        <f>COUNT(F7:F13)</f>
+        <v>7</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="5:8" x14ac:dyDescent="0.4">
+      <c r="E22" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="5:8" x14ac:dyDescent="0.4">
+      <c r="E23" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="G23" s="15" t="s">
         <v>27</v>
       </c>
+      <c r="H23" s="24" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E7" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="21">
-        <v>120</v>
-      </c>
-      <c r="H7" s="27">
-        <v>1.08</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E8" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="11">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E9" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="11">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E10" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="11">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E11" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="11">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E12" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" s="11">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E13" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="F13" s="11">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E15" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E16" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F16" s="8">
-        <f>SUM(Table1[header2])</f>
-        <v>850</v>
-      </c>
-    </row>
-    <row r="17" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E17" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F17" s="9">
-        <f>AVERAGE(Table1[header2])</f>
-        <v>121.42857142857143</v>
-      </c>
-    </row>
-    <row r="18" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E18" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F18" s="9">
-        <f>MAX(Table1[header2])</f>
-        <v>142</v>
-      </c>
-    </row>
-    <row r="19" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E19" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F19" s="9">
-        <f>MIN(Table1[header2])</f>
-        <v>98</v>
-      </c>
-    </row>
-    <row r="20" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E20" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F20" s="10">
-        <f>COUNT(Table1[header2])</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E22" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E23" s="18" t="s">
+    <row r="24" spans="5:8" x14ac:dyDescent="0.4">
+      <c r="E24" s="11" t="s">
         <v>8</v>
-      </c>
-      <c r="F23" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="G23" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="H23" s="25" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="24" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E24" s="12" t="s">
-        <v>9</v>
       </c>
       <c r="F24" s="8">
         <f>F7</f>
         <v>120</v>
       </c>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
+      <c r="G24" s="25">
+        <f>CONVERT(F24,"kWh","J")</f>
+        <v>432000000</v>
+      </c>
+      <c r="H24" s="26">
+        <f>F24*$H$7</f>
+        <v>129.60000000000002</v>
+      </c>
     </row>
-    <row r="25" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E25" s="14" t="s">
-        <v>10</v>
+    <row r="25" spans="5:8" x14ac:dyDescent="0.4">
+      <c r="E25" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="F25" s="9">
         <f t="shared" ref="F25:F30" si="0">F8</f>
         <v>135</v>
       </c>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
+      <c r="G25" s="22">
+        <f t="shared" ref="G25:G30" si="1">CONVERT(F25,"kWh","J")</f>
+        <v>486000000</v>
+      </c>
+      <c r="H25" s="27">
+        <f t="shared" ref="H25:H30" si="2">F25*$H$7</f>
+        <v>145.80000000000001</v>
+      </c>
     </row>
-    <row r="26" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E26" s="14" t="s">
-        <v>11</v>
+    <row r="26" spans="5:8" x14ac:dyDescent="0.4">
+      <c r="E26" s="12" t="s">
+        <v>10</v>
       </c>
       <c r="F26" s="9">
         <f t="shared" si="0"/>
         <v>128</v>
       </c>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
+      <c r="G26" s="22">
+        <f t="shared" si="1"/>
+        <v>460800000</v>
+      </c>
+      <c r="H26" s="27">
+        <f t="shared" si="2"/>
+        <v>138.24</v>
+      </c>
     </row>
-    <row r="27" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E27" s="14" t="s">
-        <v>12</v>
+    <row r="27" spans="5:8" x14ac:dyDescent="0.4">
+      <c r="E27" s="12" t="s">
+        <v>11</v>
       </c>
       <c r="F27" s="9">
         <f t="shared" si="0"/>
         <v>142</v>
       </c>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
+      <c r="G27" s="22">
+        <f t="shared" si="1"/>
+        <v>511200000</v>
+      </c>
+      <c r="H27" s="27">
+        <f t="shared" si="2"/>
+        <v>153.36000000000001</v>
+      </c>
     </row>
-    <row r="28" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E28" s="14" t="s">
-        <v>13</v>
+    <row r="28" spans="5:8" x14ac:dyDescent="0.4">
+      <c r="E28" s="12" t="s">
+        <v>12</v>
       </c>
       <c r="F28" s="9">
         <f t="shared" si="0"/>
         <v>115</v>
       </c>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
+      <c r="G28" s="22">
+        <f t="shared" si="1"/>
+        <v>414000000</v>
+      </c>
+      <c r="H28" s="27">
+        <f t="shared" si="2"/>
+        <v>124.2</v>
+      </c>
     </row>
-    <row r="29" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E29" s="14" t="s">
-        <v>14</v>
+    <row r="29" spans="5:8" x14ac:dyDescent="0.4">
+      <c r="E29" s="12" t="s">
+        <v>13</v>
       </c>
       <c r="F29" s="9">
         <f t="shared" si="0"/>
         <v>98</v>
       </c>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
+      <c r="G29" s="22">
+        <f t="shared" si="1"/>
+        <v>352800000</v>
+      </c>
+      <c r="H29" s="27">
+        <f t="shared" si="2"/>
+        <v>105.84</v>
+      </c>
     </row>
-    <row r="30" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E30" s="16" t="s">
-        <v>15</v>
+    <row r="30" spans="5:8" x14ac:dyDescent="0.4">
+      <c r="E30" s="13" t="s">
+        <v>14</v>
       </c>
       <c r="F30" s="10">
         <f t="shared" si="0"/>
         <v>112</v>
       </c>
-      <c r="G30" s="17"/>
-      <c r="H30" s="17"/>
+      <c r="G30" s="23">
+        <f t="shared" si="1"/>
+        <v>403200000</v>
+      </c>
+      <c r="H30" s="28">
+        <f t="shared" si="2"/>
+        <v>120.96000000000001</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B6" r:id="rId1" xr:uid="{10C7ED9E-B055-4A34-B53E-AB9793D21924}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId2"/>
-  </tableParts>
+  <pageSetup scale="60" orientation="landscape" r:id="rId2"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>